--- a/content/source/hotico-content-ro.xlsx
+++ b/content/source/hotico-content-ro.xlsx
@@ -22,76 +22,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="266">
   <si>
+    <t>titlu video</t>
+  </si>
+  <si>
     <t>Denumire</t>
   </si>
   <si>
-    <t>titlu video</t>
+    <t>Reconstrucția areolei prin dermopigmentare.</t>
+  </si>
+  <si>
+    <t>Link youtube</t>
+  </si>
+  <si>
+    <t>link vimeo</t>
+  </si>
+  <si>
+    <t>Mini meniu servicii</t>
   </si>
   <si>
     <t>descriere CTA (scris sub) Video</t>
   </si>
   <si>
-    <t>Link youtube</t>
-  </si>
-  <si>
-    <t>Reconstrucția areolei prin dermopigmentare.</t>
-  </si>
-  <si>
-    <t>link vimeo</t>
+    <t xml:space="preserve">cta sub titlu </t>
+  </si>
+  <si>
+    <t>Află cum arta dermopigmentării poate închide cu blândețe un capitol dureros.</t>
+  </si>
+  <si>
+    <t>Reconstrucția sprâncenelor și Eyelinerului în cazul Alopeciei</t>
+  </si>
+  <si>
+    <t>Detalii</t>
+  </si>
+  <si>
+    <t>cta intrebari</t>
   </si>
   <si>
     <t>descriere text</t>
   </si>
   <si>
+    <t>Am adunat aici cele mai importante întrebări și răspunsurile care te vor ajuta să înțelegi procedura pas cu pas. Dă click pe întrebare și video-ul te va purta exact acolo unde ofer explicația completă.</t>
+  </si>
+  <si>
+    <t>link youtube</t>
+  </si>
+  <si>
     <t>Despre HOTICO</t>
   </si>
   <si>
+    <t>Preț</t>
+  </si>
+  <si>
+    <t>Ce este reconstrucția areolei prin dermopigmentare?</t>
+  </si>
+  <si>
     <t>Cum poate dermopigmentarea să aducă frumusețe naturală, vindecare emoțională și putere personală? Descoperă răspunsul în acest video manifest semnat Alexandra Hotico.</t>
   </si>
   <si>
-    <t>Mini meniu servicii</t>
-  </si>
-  <si>
-    <t>https://youtu.be/dHhHdFYaQBY</t>
-  </si>
-  <si>
-    <t>Reconstrucția sprâncenelor și Eyelinerului în cazul Alopeciei</t>
-  </si>
-  <si>
-    <t>link youtube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cta sub titlu </t>
-  </si>
-  <si>
-    <t>Află cum arta dermopigmentării poate închide cu blândețe un capitol dureros.</t>
-  </si>
-  <si>
-    <t>Detalii</t>
-  </si>
-  <si>
     <t>Află cum grija pentru o linie trasată fin poate aduce înapoi expresia ta unică.</t>
-  </si>
-  <si>
-    <t>cta intrebari</t>
-  </si>
-  <si>
-    <t>Am adunat aici cele mai importante întrebări și răspunsurile care te vor ajuta să înțelegi procedura pas cu pas. Dă click pe întrebare și video-ul te va purta exact acolo unde ofer explicația completă.</t>
-  </si>
-  <si>
-    <t>Preț</t>
-  </si>
-  <si>
-    <t>Am strâns cele mai importante întrebări și răspunsuri despre procedura dedicată alopeciei, ca să poți înțelege în detaliu cum redăm expresia naturală a feței. Dă click pe întrebare și lasă-mă să te ghidez pas cu pas prin video, dar și text.</t>
-  </si>
-  <si>
-    <t>Ce este reconstrucția areolei prin dermopigmentare?</t>
-  </si>
-  <si>
-    <t>Ce înseamnă dermopigmentarea în cazul alopeciei?</t>
-  </si>
-  <si>
-    <t>Camuflajul cicatricilor prin dermopigmentare paramedicală</t>
   </si>
   <si>
     <t>Sunt momente în viață când corpul nostru trece prin schimbări profunde, iar pielea rămâne cu urme care spun povești grele. Pentru multe femei, pierderea areolei după o mastectomie sau altă intervenție chirurgicală nu este doar o schimbare fizică, ci și una emoțională, care poate afecta felul în care se văd și se simt.
@@ -101,7 +89,16 @@
 Rezultatul nu este doar vizibil în oglindă — este simțit în modul în care te percepi pe tine însăți. Pentru multe femei, aceasta este ultima etapă în procesul de vindecare și reconectare cu propriul corp, un moment în care se pot privi din nou cu încredere și liniște.</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134399482/6fcdcaf1c3?share=copy&amp;fl=sv&amp;fe=ci</t>
+    <t>Am strâns cele mai importante întrebări și răspunsuri despre procedura dedicată alopeciei, ca să poți înțelege în detaliu cum redăm expresia naturală a feței. Dă click pe întrebare și lasă-mă să te ghidez pas cu pas prin video, dar și text.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yQ7k5kYULIw?t=26</t>
+  </si>
+  <si>
+    <t>https://youtu.be/dHhHdFYaQBY</t>
+  </si>
+  <si>
+    <t>Ce înseamnă dermopigmentarea în cazul alopeciei?</t>
   </si>
   <si>
     <t>Când alopecia îți schimbă chipul și îți ia sprâncenele sau genele, nu pierzi doar fire de păr, pierzi o parte din expresia ta, din felul în care te recunoști în oglindă. Pentru multe persoane, această schimbare aduce nesiguranță, dar și dorința de a-și recăpăta trăsăturile familiare.
@@ -111,32 +108,73 @@
 Rezultatul final nu este doar un chip cu sprâncene și privire conturată este un pas spre a te regăsi, spre a-ți recăpăta expresia care îți este atât de dragă și spre a te simți din nou tu.</t>
   </si>
   <si>
-    <t>https://youtu.be/yQ7k5kYULIw?t=26</t>
-  </si>
-  <si>
-    <t>Descoperă cum fiecare nuanță atent aleasă poate estompa cu blândețe urmele trecutului.</t>
-  </si>
-  <si>
     <t>https://youtu.be/ghkyuPTiqAU</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ți-am pregătit cele mai importante întrebări și răspunsuri despre camuflarea cicatricilor, explicate clar, atât în text, cât și în video, ca să știi exact la ce să te aștepți de la această procedură.</t>
-  </si>
-  <si>
-    <t>Ce este camuflajul cicatricilor prin dermopigmentare?</t>
-  </si>
-  <si>
-    <t>Fiecare cicatrice are o poveste. Unele vorbesc despre vindecare, altele despre accidente sau intervenții care ți-au schimbat viața. Dar indiferent de cum au apărut: după o operație, o rană, un accident, o arsură sau chiar din naștere, cum este cazul cleft lip (buza despărțită), toate pot aduce cu ele amintiri pe care poate nu îți dorești să le vezi zilnic în oglindă.
-Camuflajul cicatricilor prin dermopigmentare este o tehnică specializată prin care uniformizez culoarea pielii din zona cicatricii, pentru ca aceasta să se integreze cât mai natural cu pielea din jur. Folosesc un dermograf profesional și pigmenți medicali, formulați pentru a se adapta tonului tău de piele, astfel încât rezultatul să fie discret și armonios.
-Procedura poate fi aplicată pentru cicatrici plate și vindecate complet, inclusiv pentru cele rezultate din intervenții chirurgicale, cezariană, reconstrucții, răni, accidente, arsuri, dar și pentru cicatricile rezultate din cleft lip. În acest tip de lucrări, precizia tehnică se îmbină cu o evaluare atentă a nuanțelor pielii, pentru a obține un efect cât mai natural.
-Înainte de a începe, discutăm despre istoricul cicatricii, despre așteptări și despre ce este realist să obținem, pentru că fiecare tip de piele reacționează diferit. Lucrez cu răbdare și în pași mici, pentru a respecta integritatea pielii și a obține un rezultat durabil și plăcut vizual.
-Rezultatul final? O piele cu un aspect mai uniform, în care cicatricea devine mult mai puțin vizibilă, iar tu poți să îți privești corpul cu mai multă liniște și încredere.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/HubjqYkzxww?t=29</t>
+    <t>https://vimeo.com/1134193056/4b9c46e8ad?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t>https://vimeo.com/1134294268/c2e80a3ae2?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Galerie</t>
+  </si>
+  <si>
+    <t>Ce fel de pigmenți folosesc?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Armonie între știință, artă, empatie și feminitate.</t>
+  </si>
+  <si>
+    <t>Când lucrez cu persoane care au alopecie, știu că alegerea pigmentului nu e doar o chestiune estetică, ci și una de durabilitate și siguranță. Pielea afectată de alopecie poate reacționa diferit la pigment, în funcție de cauza acestei afecțiuni, fie ea autoimună, hormonală, ereditară sau legată de tratamente medicale.
+La sprâncene, aleg pigmenți cosmetici hipoalergenici, fără metale grele, formulați special pentru a rămâne stabili și a se estompa frumos în timp. Îmi adaptez întotdeauna selecția în funcție de subtonul pielii tale și de eventualele particularități cauzate de alopecie. Dacă, de exemplu, știu că metabolismul tău celular e mai rapid din cauza unei condiții medicale, aleg pigmenți cu o concentrație de culoare mai ridicată, astfel încât rezultatul să rămână armonios cât mai mult timp.
+La eyeliner, folosesc pigmenți cu o stabilitate excelentă, rezistenți la oxidare și la modificări de nuanță, pentru că zona ochilor are o piele mai fină, dar și pentru că vreau ca linia să rămână clară și intensă chiar și după câțiva ani.
+În ambele cazuri, pigmenții sunt testați dermatologic, certificați pentru uz cosmetic și selectați astfel încât să-ți ofere frumusețe imediată, dar și siguranța că rezultatul va rămâne curat, natural și elegant pe termen lung, indiferent de tipul tău de alopecie.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CgxXj417O9g?t=25</t>
+  </si>
+  <si>
+    <t>Ce fel de pigmenti folosesc si cum ii personalizez pentru tine?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Când vine vorba de dermopigmentarea areolei, alegerea pigmentului nu este doar o chestiune de estetică — este o promisiune de stabilitate și de respect față de parcursul tău de vindecare.
+Lucrez exclusiv cu pigmenți paramedicali permanenți, formulați special pentru reconstrucția areolei. Sunt pigmenți organici, stabili în timp, care își păstrează nuanța și intensitatea ani la rând. De ce este atât de important? Pentru că în cazul areolei, nu ne dorim ca în câțiva ani culoarea să se estompeze sau forma clar creată să se piardă. Este o zonă care nu își schimbă poziția odată cu trecerea timpului, iar reconstrucția trebuie să fie durabilă, astfel încât rezultatul să rămână natural și armonios pe termen lung.
+</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fbxgtEbAggk</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134399482/6fcdcaf1c3?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134295512/1bc1955d2e?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134269658/fa56a674be?fl=tl&amp;fe=ec</t>
+  </si>
+  <si>
+    <t>E procedura  dureroasă?</t>
+  </si>
+  <si>
+    <t>Știu că este una dintre primele întrebări care îți trec prin minte înainte să programezi o procedură. Și e normal, nimeni nu își dorește să treacă prin disconfort inutil.
+Adevărul este că fiecare persoană simte diferit. Unele cliente îmi spun că li se pare doar o senzație ușoară, ca o zgârietură fină sau furnicături blânde. Altele pot simți un pic mai intens, dar foarte rar cineva descrie procedura ca fiind dureroasă.
+Față de tatuajele clasice, dermopigmentarea cosmetică sau paramedicală lucrează doar în straturile superficiale ale pielii, ceea ce înseamnă automat mai puțin disconfort.
+În plus, folosesc anestezice topice: creme, geluri sau lichide aplicate direct pe piele care au rolul de a face tot procesul cât mai confortabil. Acestea pot conține:
+Lidocaină, pentru amorțire rapidă,
+Tetracaină, pentru un efect mai profund,
+Benzocaină, uneori combinată cu celelalte,
+și epinefrină, care reduce sângerarea și inflamația și prelungește efectul anestezic.
+Pe tot parcursul lucrului, sunt atentă la cum te simți. Dacă e nevoie, pot aplica suplimentar anestezic, astfel încât să lucrăm în ritmul tău și cu toată grija pentru corpul tău.
+Pe scurt: nu este complet lipsită de senzații, dar este o procedură gândită să fie blândă, sigură și suportabilă, astfel încât experiența ta să fie cât mai relaxată și lipsită de stres.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Qbq0hvdhrlw</t>
+  </si>
+  <si>
+    <t>E procedura dureroasa?</t>
   </si>
   <si>
     <t xml:space="preserve">Sunt fondatoarea HOTICO - Institut de Restaurare. De peste opt ani lucrez în domeniul dermopigmentării reparatorii și al machiajului permanent, din vocație.
@@ -151,10 +189,22 @@
     <t>Cum lucrează HOTICO</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134193056/4b9c46e8ad?share=copy&amp;fl=sv&amp;fe=ci</t>
+    <t>Știu că este una dintre primele întrebări care îți trec prin minte înainte să programezi o procedură. Și e normal, nimeni nu își dorește să treacă prin disconfort inutil.
+Adevărul este că fiecare persoană simte diferit. Unele cliente îmi spun că li se pare doar o senzație ușoară, ca o zgârietură fină sau furnicături blânde. Altele pot simți un pic mai intens, dar foarte rar cineva descrie procedura ca fiind dureroasă.
+Față de tatuajele clasice, dermopigmentarea cosmetică sau paramedicală lucrează doar în straturile superficiale ale pielii, ceea ce înseamnă automat mai puțin disconfort.
+În plus, folosesc anestezice topice: creme, geluri sau lichide aplicate direct pe piele, care au rolul de a face tot procesul cât mai confortabil. Acestea pot conține:
+Lidocaină, pentru amorțire rapidă,
+Tetracaină, pentru un efect mai profund,
+Benzocaină, uneori combinată cu celelalte,
+și epinefrină, care reduce sângerarea și inflamația și prelungește efectul anestezic.
+Pe tot parcursul lucrului, sunt atentă la cum te simți. Dacă e nevoie, pot aplica suplimentar anestezic, astfel încât să lucrăm în ritmul tău și cu toată grija pentru corpul tău.
+Pe scurt: nu este complet lipsită de senzații, dar este o procedură gândită să fie blândă, sigură și suportabilă, astfel încât experiența ta să fie cât mai relaxată și lipsită de stres.</t>
   </si>
   <si>
     <t>Descoperă cum fiecare procedură începe cu tine, povestea ta și un proces personalizat, sigur și empatic</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134367682/92d4adaa32?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <r>
@@ -170,152 +220,10 @@
     </r>
   </si>
   <si>
-    <t>Galerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Armonie între știință, artă, empatie și feminitate.</t>
-  </si>
-  <si>
     <t>https://vimeo.com/1134399977/2169ab1004?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134390484/703fcfc3bf?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Ce fel de pigmenți folosesc?</t>
-  </si>
-  <si>
-    <t>Când lucrez cu persoane care au alopecie, știu că alegerea pigmentului nu e doar o chestiune estetică, ci și una de durabilitate și siguranță. Pielea afectată de alopecie poate reacționa diferit la pigment, în funcție de cauza acestei afecțiuni, fie ea autoimună, hormonală, ereditară sau legată de tratamente medicale.
-La sprâncene, aleg pigmenți cosmetici hipoalergenici, fără metale grele, formulați special pentru a rămâne stabili și a se estompa frumos în timp. Îmi adaptez întotdeauna selecția în funcție de subtonul pielii tale și de eventualele particularități cauzate de alopecie. Dacă, de exemplu, știu că metabolismul tău celular e mai rapid din cauza unei condiții medicale, aleg pigmenți cu o concentrație de culoare mai ridicată, astfel încât rezultatul să rămână armonios cât mai mult timp.
-La eyeliner, folosesc pigmenți cu o stabilitate excelentă, rezistenți la oxidare și la modificări de nuanță, pentru că zona ochilor are o piele mai fină, dar și pentru că vreau ca linia să rămână clară și intensă chiar și după câțiva ani.
-În ambele cazuri, pigmenții sunt testați dermatologic, certificați pentru uz cosmetic și selectați astfel încât să-ți ofere frumusețe imediată, dar și siguranța că rezultatul va rămâne curat, natural și elegant pe termen lung, indiferent de tipul tău de alopecie.</t>
-  </si>
-  <si>
-    <t>Ce fel de pigmenti folosesc si cum ii personalizez pentru tine?</t>
-  </si>
-  <si>
-    <t>https://youtu.be/CgxXj417O9g?t=25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Când vine vorba de dermopigmentarea areolei, alegerea pigmentului nu este doar o chestiune de estetică — este o promisiune de stabilitate și de respect față de parcursul tău de vindecare.
-Lucrez exclusiv cu pigmenți paramedicali permanenți, formulați special pentru reconstrucția areolei. Sunt pigmenți organici, stabili în timp, care își păstrează nuanța și intensitatea ani la rând. De ce este atât de important? Pentru că în cazul areolei, nu ne dorim ca în câțiva ani culoarea să se estompeze sau forma clar creată să se piardă. Este o zonă care nu își schimbă poziția odată cu trecerea timpului, iar reconstrucția trebuie să fie durabilă, astfel încât rezultatul să rămână natural și armonios pe termen lung.
-</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fbxgtEbAggk</t>
-  </si>
-  <si>
-    <t>Totul începe cu tine și cu povestea ta. La consultația prealabilă te ascult și înțeleg ce îți dorești. Fiecare rezultat se construiește pe trăsăturile tale, în tonul pielii, cu istoricul medical și în ritmul tău.
-Folosesc pigmenți formulați special pentru dermopigmentare cosmetică și paramedicală, siguri medical și testați pentru stabilitate în timp și palete largi de tonuri și subtonuri care permit alegerea sau chiar pregătirea personalizată a unor nuanțe care să se integreze natural în piele.
-Aparatura de ultimă generație, instrumentele sterile și de unică folosință, iar protocoalele de igienă respectă standardele elvețiene și internaționale.
-Lucrez fără grabă, astfel încât fiecare etapă să fie exact cum îți dorești și ca pielea ta să aibă timp să se refacă. Standardele înalte sunt singura variantă. Te tratez ca pe o persoană foarte dragă mie.
-Când te așezi pe patul meu, respiri adânc și lași totul în grija mea. Ești pe mâini sigure, de la alegerea pigmentului până la ultima linie trasată și recomandările de întreținere a procedurii.</t>
-  </si>
-  <si>
-    <t>Învață cu HOTICO</t>
-  </si>
-  <si>
-    <t>Află de ce dermopigmentarea paramedicală este viitorul meseriei tale și cum un training dedicat îți poate schimba parcursul profesional.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rszEkC_G3h4</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134269658/fa56a674be?fl=tl&amp;fe=ec</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134295512/1bc1955d2e?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134403298/ebf7333828?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>ce fel de pigmenti folosesc?</t>
-  </si>
-  <si>
-    <t>Când lucram pe cicatrici, e vorba de a acoperi o zonă, dar si  de a o integra perfect în restul pielii, astfel încât să nu mai atragă atenția. Asta înseamnă că pigmentul trebuie ales cu o precizie extremă, atât ca nuanță, cât și ca formulă.
-Folosesc pigmenți special concepuți pentru camuflaj paramedical, hipoalergenici, fără metale grele, formulați pentru a fi biocompatibili cu pielea umană. Acești pigmenți nu sunt culori simple dintr-o cutie: îi combin personalizat, în funcție de tonul și subtonul pielii tale, dar și de particularitățile cicatricii.
-Pentru cicatricile mai vechi și complet vindecate, formula pigmentului poate fi mai bogată în tonuri calde sau reci, pentru a contrabalansa nuanța pe care o are cicatricea în mod natural. În cazul cicatricilor rezultate din intervenții chirurgicale, accidente sau afecțiuni precum despicătura de buză (cleft lip), mă asigur că pigmentul ales rămâne stabil și se estompează uniform, fără să capete tonuri nedorite în timp.
-Rezistența culorii poate fi influențată și de textura cicatricii, zonele mai fibroase pot reține diferit pigmentul,  motiv pentru care ajustez concentrația și tehnica de implantare. Toate aceste detalii fac parte dintr-un proces atent, în care scopul meu e să creez o armonie vizuală care să îți redea încrederea în tine.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/sUWovJxULxo?t=11</t>
-  </si>
-  <si>
-    <t>E procedura dureroasa?</t>
-  </si>
-  <si>
-    <t>E procedura  dureroasă?</t>
-  </si>
-  <si>
-    <t>Știu că este una dintre primele întrebări care îți trec prin minte înainte să programezi o procedură. Și e normal, nimeni nu își dorește să treacă prin disconfort inutil.
-Adevărul este că fiecare persoană simte diferit. Unele cliente îmi spun că li se pare doar o senzație ușoară, ca o zgârietură fină sau furnicături blânde. Altele pot simți un pic mai intens, dar foarte rar cineva descrie procedura ca fiind dureroasă.
-Față de tatuajele clasice, dermopigmentarea cosmetică sau paramedicală lucrează doar în straturile superficiale ale pielii, ceea ce înseamnă automat mai puțin disconfort.
-În plus, folosesc anestezice topice: creme, geluri sau lichide aplicate direct pe piele, care au rolul de a face tot procesul cât mai confortabil. Acestea pot conține:
-Lidocaină, pentru amorțire rapidă,
-Tetracaină, pentru un efect mai profund,
-Benzocaină, uneori combinată cu celelalte,
-și epinefrină, care reduce sângerarea și inflamația și prelungește efectul anestezic.
-Pe tot parcursul lucrului, sunt atentă la cum te simți. Dacă e nevoie, pot aplica suplimentar anestezic, astfel încât să lucrăm în ritmul tău și cu toată grija pentru corpul tău.
-Pe scurt: nu este complet lipsită de senzații, dar este o procedură gândită să fie blândă, sigură și suportabilă, astfel încât experiența ta să fie cât mai relaxată și lipsită de stres.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Qbq0hvdhrlw</t>
-  </si>
-  <si>
-    <t>Știu că este una dintre primele întrebări care îți trec prin minte înainte să programezi o procedură. Și e normal, nimeni nu își dorește să treacă prin disconfort inutil.
-Adevărul este că fiecare persoană simte diferit. Unele cliente îmi spun că li se pare doar o senzație ușoară, ca o zgârietură fină sau furnicături blânde. Altele pot simți un pic mai intens, dar foarte rar cineva descrie procedura ca fiind dureroasă.
-Față de tatuajele clasice, dermopigmentarea cosmetică sau paramedicală lucrează doar în straturile superficiale ale pielii, ceea ce înseamnă automat mai puțin disconfort.
-În plus, folosesc anestezice topice: creme, geluri sau lichide aplicate direct pe piele care au rolul de a face tot procesul cât mai confortabil. Acestea pot conține:
-Lidocaină, pentru amorțire rapidă,
-Tetracaină, pentru un efect mai profund,
-Benzocaină, uneori combinată cu celelalte,
-și epinefrină, care reduce sângerarea și inflamația și prelungește efectul anestezic.
-Pe tot parcursul lucrului, sunt atentă la cum te simți. Dacă e nevoie, pot aplica suplimentar anestezic, astfel încât să lucrăm în ritmul tău și cu toată grija pentru corpul tău.
-Pe scurt: nu este complet lipsită de senzații, dar este o procedură gândită să fie blândă, sigură și suportabilă, astfel încât experiența ta să fie cât mai relaxată și lipsită de stres.</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134390997/593494e586?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134367682/92d4adaa32?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Anii de lucru cu femei după mastectomie, operații sau accidente m-au învățat că o procedură făcută cu precizie schimbă felul în care cineva se vede.
-Vin cu tehnică perfecționată în ani de practică, cu înțelegerea contextului medical și cu o abordare umană pe care o înveți doar lângă cliente. Îți arăt cum să devii specialistul căutat pentru proceduri delicate.
-Dermopigmentarea paramedicală te conectează cu medici, clinici și ONG-uri și te așază într-un segment cu cerere mare și concurență redusă. Vii din altă zonă de beauty și descoperi o meserie cu sens, în care fiecare procedură e o poveste de reconstrucție și un pas spre reapropierea imaginii de sine.
-Îți dau protocoale sigure, tehnici adaptate fiecărui tip de piele și comunicarea cu cliente vulnerabile. Termini cursul cu mâna sigură pe camuflajul cicatricilor și reconstrucția areolei mamare. Clientele simt asta din prima ședință, iar încrederea lor devine capitalul tău.</t>
-  </si>
-  <si>
-    <t>Ce e Dermopigmentarea Paramedicala?</t>
-  </si>
-  <si>
-    <t>Descoperă pas cu pas unde se aplică dermopigmentarea paramedicală și de ce are un impact emoțional uriaș.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/R0d-AAGRoPk</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134400718/64a5e649de?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Procedura e dureroasa?</t>
-  </si>
-  <si>
     <t>Ce trebuie să fac înainte de procedură?</t>
-  </si>
-  <si>
-    <t>Se poate face dacă alăptez?</t>
-  </si>
-  <si>
-    <t>Este una dintre întrebările pe care le primesc cel mai des, și vreau să îți răspund sincer și complet. În teorie, dermopigmentarea cosmetică acționează doar în straturile superficiale ale pielii, folosind pigmenți biocompatibili și anestezice locale aplicate pe suprafață. Lucrez cu consumabile sterile, de unică folosință, într-un mediu care respectă toate normele de igienă și siguranță.
-Cu toate acestea, conform recomandărilor de bune practici, toate procedurile estetice, inclusiv dermopigmentarea, sunt contraindicate în perioada sarcinii și alăptării. Motivul? Principiul de precauție. Chiar dacă riscul de reacții adverse este redus, corpul trece prin schimbări hormonale și fiziologice importante, iar orice stres suplimentar sau reacție locală poate influența starea ta generală și, indirect, alăptarea.
-Recomandarea mea, ca profesionist, este să amâni procedura până după finalul alăptării sau cel puțin până în ultimele luni, când hrănirea la sân nu mai este exclusivă. Este cea mai sigură alegere atât pentru tine, cât și pentru bebelușul tău.
-Siguranța și sănătatea ta sunt mereu pe primul loc. Dermopigmentarea este despre frumusețe, dar mai ales despre grijă, responsabilitate și respect pentru corpul tău.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/UCzGcLsOzk0?t=8</t>
   </si>
   <si>
     <t>„Ce trebuie să faci înainte de dermopigmentarea areolei”
@@ -329,42 +237,47 @@
 Pregătirea înainte de dermopigmentarea areolei nu este doar un pas tehnic, ci și unul emoțional. Este momentul în care îți pregătești corpul și mintea pentru o schimbare care, de multe ori, marchează sfârșitul unui capitol dificil și începutul unuia nou. Iar eu sunt aici să fac ca acest moment să fie nu doar frumos, ci și în siguranță deplină.</t>
   </si>
   <si>
-    <t>Dermopigmentarea paramedicală redă aspectul pielii după o traumă, o operație sau o afecțiune medicală, cu pigmenți și tehnici avansate.
-O întâlnești în reconstrucția areolei după mastectomie, în camuflajul cicatricilor, în uniformizarea pielii cu vitiligo stabil și în redarea sprâncenelor și a genelor pierdute. Dermopigmentarea cosmetică pune în valoare trăsăturile. Cea paramedicală îți redă identitatea.
-Pigmenții stau în stratul superficial al pielii și se integrează natural în tonul tău, fără culori tari, fără margini vizibile. Rezultatul e durabil și se estompează treptat, deci îl putem ajusta dacă pielea sau nevoile tale se schimbă.
-Lucrez cu aparatură de ultimă generație, pigmenți de calitate medicală și protocoale stricte de igienă. Fiecare lucrare e adaptată pielii și poveștii tale.
-Te privești în oglindă și te recunoști. E începutul unui capitol în care corpul tău și povestea ta merg mai departe, pe termenii tăi.</t>
-  </si>
-  <si>
     <t>https://youtu.be/QeiZ89HqCVI</t>
   </si>
   <si>
-    <t>Ce e Dermopigmentarea Cosmetica?</t>
-  </si>
-  <si>
-    <t>Descoperă cum dermopigmentarea cosmetică îți pune în valoare frumusețea naturală, discret și armonios, fără efect de tatuaj.</t>
-  </si>
-  <si>
     <t>https://vimeo.com/1134294704/d0db80d975?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://youtu.be/JS4aXaBOwRE</t>
+    <t>Se poate face dacă alăptez?</t>
+  </si>
+  <si>
+    <t>Este una dintre întrebările pe care le primesc cel mai des, și vreau să îți răspund sincer și complet. În teorie, dermopigmentarea cosmetică acționează doar în straturile superficiale ale pielii, folosind pigmenți biocompatibili și anestezice locale aplicate pe suprafață. Lucrez cu consumabile sterile, de unică folosință, într-un mediu care respectă toate normele de igienă și siguranță.
+Cu toate acestea, conform recomandărilor de bune practici, toate procedurile estetice, inclusiv dermopigmentarea, sunt contraindicate în perioada sarcinii și alăptării. Motivul? Principiul de precauție. Chiar dacă riscul de reacții adverse este redus, corpul trece prin schimbări hormonale și fiziologice importante, iar orice stres suplimentar sau reacție locală poate influența starea ta generală și, indirect, alăptarea.
+Recomandarea mea, ca profesionist, este să amâni procedura până după finalul alăptării sau cel puțin până în ultimele luni, când hrănirea la sân nu mai este exclusivă. Este cea mai sigură alegere atât pentru tine, cât și pentru bebelușul tău.
+Siguranța și sănătatea ta sunt mereu pe primul loc. Dermopigmentarea este despre frumusețe, dar mai ales despre grijă, responsabilitate și respect pentru corpul tău.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UCzGcLsOzk0?t=8</t>
+  </si>
+  <si>
+    <t>Totul începe cu tine și cu povestea ta. La consultația prealabilă te ascult și înțeleg ce îți dorești. Fiecare rezultat se construiește pe trăsăturile tale, în tonul pielii, cu istoricul medical și în ritmul tău.
+Folosesc pigmenți formulați special pentru dermopigmentare cosmetică și paramedicală, siguri medical și testați pentru stabilitate în timp și palete largi de tonuri și subtonuri care permit alegerea sau chiar pregătirea personalizată a unor nuanțe care să se integreze natural în piele.
+Aparatura de ultimă generație, instrumentele sterile și de unică folosință, iar protocoalele de igienă respectă standardele elvețiene și internaționale.
+Lucrez fără grabă, astfel încât fiecare etapă să fie exact cum îți dorești și ca pielea ta să aibă timp să se refacă. Standardele înalte sunt singura variantă. Te tratez ca pe o persoană foarte dragă mie.
+Când te așezi pe patul meu, respiri adânc și lași totul în grija mea. Ești pe mâini sigure, de la alegerea pigmentului până la ultima linie trasată și recomandările de întreținere a procedurii.</t>
+  </si>
+  <si>
+    <t>Învață cu HOTICO</t>
+  </si>
+  <si>
+    <t>Află de ce dermopigmentarea paramedicală este viitorul meseriei tale și cum un training dedicat îți poate schimba parcursul profesional.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rszEkC_G3h4</t>
+  </si>
+  <si>
+    <t>Ce se întâmplă imediat după și cum întrețin procedura?</t>
   </si>
   <si>
     <t>https://vimeo.com/1134366815/66b2b7f34d?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134400348/0442726a1f?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Ce se întâmplă imediat după și cum întrețin procedura?</t>
-  </si>
-  <si>
-    <t>Dermopigmentarea cosmetică e o procedură fină prin care introduc pigmenți în stratul superficial al pielii, ca să îți armonizez trăsăturile. O mai auzi numită machiaj semi-permanent sau micropigmentare și se face cel mai des pentru sprâncene, buze și eyeliner.
-Pigmenții rămân la suprafață și se estompează treptat, deci în timp ești liberă să schimbi rezultatul. Sunt formulați special pentru față, respectă tonul pielii și dau un aspect natural.
-Tehnica îți pune în valoare frumusețea naturală. Redă forma sprâncenelor, luminează și uniformizează culoarea buzelor, accentuează discret linia genelor.
-Lucrez cu aparatură de ultimă generație și pigmenți de calitate medicală, aleși după tonul pielii. Rezultatul ține între 1 și 3 ani, în funcție de tipul pielii, apoi facem o ședință de reîmprospătare.
-Câștigi timpul de dimineață. Te trezești cu chipul deja gata, te privești în oglindă și te vezi odihnită, exact tu, puțin mai clară.</t>
+    <t>https://vimeo.com/1134403298/ebf7333828?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -377,18 +290,129 @@
 Eu voi fi alături de tine și după procedură, pentru a mă asigura că rezultatul rămâne uniform, frumos și stabil în timp. Îngrijirea corectă în primele săptămâni face toată diferența pentru un efect natural și armonios, de care să te bucuri ani întregi.</t>
   </si>
   <si>
+    <t>https://youtu.be/IDnRhucH9mI?t=14</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134295889/a09ca49b02?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Anii de lucru cu femei după mastectomie, operații sau accidente m-au învățat că o procedură făcută cu precizie schimbă felul în care cineva se vede.
+Vin cu tehnică perfecționată în ani de practică, cu înțelegerea contextului medical și cu o abordare umană pe care o înveți doar lângă cliente. Îți arăt cum să devii specialistul căutat pentru proceduri delicate.
+Dermopigmentarea paramedicală te conectează cu medici, clinici și ONG-uri și te așază într-un segment cu cerere mare și concurență redusă. Vii din altă zonă de beauty și descoperi o meserie cu sens, în care fiecare procedură e o poveste de reconstrucție și un pas spre reapropierea imaginii de sine.
+Îți dau protocoale sigure, tehnici adaptate fiecărui tip de piele și comunicarea cu cliente vulnerabile. Termini cursul cu mâna sigură pe camuflajul cicatricilor și reconstrucția areolei mamare. Clientele simt asta din prima ședință, iar încrederea lor devine capitalul tău.</t>
+  </si>
+  <si>
+    <t>Ce e Dermopigmentarea Paramedicala?</t>
+  </si>
+  <si>
+    <t>Descoperă pas cu pas unde se aplică dermopigmentarea paramedicală și de ce are un impact emoțional uriaș.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/R0d-AAGRoPk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Alopecia, fie ea areată, totală sau cauzată de factori medicali și tratamente precum chimioterapia, aduce cu sine provocări nu doar estetice, ci și practice. Când sprâncenele și genele lipsesc, dermopigmentarea poate reda armonia feței, expresivitatea și încrederea. Dar înainte să ajungem acolo, pregătirea corectă este esențială pentru un rezultat frumos și stabil.
+În primul rând, trebuie să știm cauza alopeciei. Dacă este de natură autoimună sau hormonală (alopecia areată, tiroidită, menopauză), pielea din zonă poate fi mai sensibilă sau cu o capacitate diferită de fixare a pigmentului. Dacă pierderea părului a fost cauzată de tratamente oncologice, este esențial să așteptăm minim 6 luni după încheierea acestora și să avem acordul medicului curant. În cazul alopeciei fără cauză medicală activă, procedura se poate face imediat ce pielea este sănătoasă.
+Hidratarea pielii este crucială, fără fire de păr, pielea sprâncenelor și a pleoapelor tinde să fie mai expusă vântului, soarelui sau frigului, ceea ce o poate usca rapid. În săptămânile de dinainte, folosește o cremă blândă, fără parfum, pentru a menține elasticitatea pielii.
+Evită procedurile agresive în zona ochilor și sprâncenelor cu cel puțin 2 săptămâni înainte: epilare cu ceară, tratamente cu acizi, microdermabraziune sau peelinguri chimice. Acestea pot irita pielea și afecta modul în care pigmentul se fixează.
+În ziua procedurii, evită cafeaua, alcoolul și aspirina sau ibuprofenul, toate pot crește sensibilitatea și riscul de sângerare. Dacă porți lentile de contact, adu și o cutiuță sterilă pentru a le păstra în timpul procedurii eyelinerului.
+În cazul alopeciei, un detaliu foarte important este designul personalizat. Nu desenăm doar o formă de sprânceană „frumoasă” și un eyeliner „plăcut vizual”, lucrăm să reconstruim expresia naturală a feței tale, ținând cont de simetrie, proporții și trăsături. Din acest motiv, în ziua programării îți voi face o simulare completă pe piele, pentru ca tu să vezi și să aprobi rezultatul înainte să începem dermopigmentarea.
+Dacă observ că pielea este iritată, extrem de uscată sau că există inflamații locale, vom reprograma. Nu este amânare, ci o alegere profesională pentru ca rezultatul să fie uniform, stabil și cu adevărat frumos.
+Pregătirea înainte de dermopigmentarea sprâncenelor și eyelinerului în cazul alopeciei este, în esență, o combinație de îngrijire fizică și claritate medicală. Iar eu sunt aici să mă asigur că atunci când ajungi pe patul meu de lucru, atât pielea ta, cât și tu, ca om, sunteți pregătiți pentru o transformare care îți va reda armonia și expresivitatea privirii.</t>
+  </si>
+  <si>
+    <t>De ce este nevoie de două ședințe?</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XGXztXrRTLc?t=24</t>
+  </si>
+  <si>
+    <t>Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
+După prima ședință de dermopigmentare, zona lucrată, fie că vorbim despre sprâncene, buze sau areole, arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
+În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
+Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
+Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ovRf93bffLc?t=12</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134400718/64a5e649de?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134367031/a78e7eed7c?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134272378/19b22a3b9a?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Dermopigmentarea paramedicală redă aspectul pielii după o traumă, o operație sau o afecțiune medicală, cu pigmenți și tehnici avansate.
+O întâlnești în reconstrucția areolei după mastectomie, în camuflajul cicatricilor, în uniformizarea pielii cu vitiligo stabil și în redarea sprâncenelor și a genelor pierdute. Dermopigmentarea cosmetică pune în valoare trăsăturile. Cea paramedicală îți redă identitatea.
+Pigmenții stau în stratul superficial al pielii și se integrează natural în tonul tău, fără culori tari, fără margini vizibile. Rezultatul e durabil și se estompează treptat, deci îl putem ajusta dacă pielea sau nevoile tale se schimbă.
+Lucrez cu aparatură de ultimă generație, pigmenți de calitate medicală și protocoale stricte de igienă. Fiecare lucrare e adaptată pielii și poveștii tale.
+Te privești în oglindă și te recunoști. E începutul unui capitol în care corpul tău și povestea ta merg mai departe, pe termenii tăi.</t>
+  </si>
+  <si>
+    <t>Ce e Dermopigmentarea Cosmetica?</t>
+  </si>
+  <si>
+    <t>Descoperă cum dermopigmentarea cosmetică îți pune în valoare frumusețea naturală, discret și armonios, fără efect de tatuaj.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JS4aXaBOwRE</t>
+  </si>
+  <si>
+    <t>Cât rezistă pigmentul?</t>
+  </si>
+  <si>
+    <t>Dermopigmentarea areolei este, prin natura și scopul ei, o procedură gândită să dureze. Folosim pigmenți organici special concepuți pentru reconstrucția areolei, aleși tocmai pentru stabilitatea lor în timp. Rezultatul? O culoare frumoasă și armonioasă, care își păstrează vitalitatea ani la rând, fără schimbări vizibile sau neplăcute.
+Spre deosebire de alte zone ale corpului, areola nu este expusă constant la soare sau factori care pot grăbi estomparea pigmentului, ceea ce contribuie la o rezistență aproape permanentă. Astfel, o singură procedură corect realizată, urmată de retușul inițial, poate aduce un rezultat de lungă durată, care să nu necesite reîmprospătări frecvente.
+Acesta este și motivul pentru care dermopigmentarea reconstructivă a areolei este considerată o etapă finală, stabilă și sigură în procesul de reconstrucție mamară — o intervenție care oferă liniște, siguranță și o imagine corporală cu care te poți simți din nou împăcată, zi după zi, an după an.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/j8PmKJ4MVAc</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134400348/0442726a1f?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>În primele ore, sprâncenele sau eyelinerul vor părea mai intense, mai închise la culoare. Este absolut normal, pigmentul este încă la suprafață și pielea răspunde la procedură. În această fază, îți voi arăta exact cum să cureți delicat zona, astfel încât să îndepărtezi excesul de limfă fără să deranjezi pielea. Foarte important este să nu atingi zona cu mâinile murdare și să eviți complet umezirea directă sau expunerea la căldură și aburi. Piscina, sauna sau dușurile fierbinți nu sunt o opțiune în prima săptămână.
+Pe măsură ce pielea începe să se regenereze, este posibil să apară mici cruste. Știu că tentația de a le desprinde poate fi mare, dar te rog să le lași să cadă singure. Dacă le îndepărtezi înainte de vreme, riști să scoți și pigmentul din piele, lăsând zone fără culoare care nu se pot corecta decât la retuș. Îți voi recomanda un balsam de vindecare special, pe care să îl aplici în strat foarte subțire, cu mâinile curate sau cu un bețișor cosmetic, de câteva ori pe zi.
+În cazul eyelinerului, este normal să simți o ușoară sensibilitate sau să observi o mică umflare a pleoapelor. O simplă compresă rece, aplicată de câteva ori pe zi, ajută enorm la calmarea zonei. La fel de important este să eviți machiajul în jurul ochilor, mascara sau produse uleioase pentru demachiere până când pielea este complet vindecată.
+Protecția solară este un alt pas pe care nu îl poți sări. Chiar și iarna, radiațiile UV pot degrada pigmentul, așa că îți recomand fie un SPF aplicat zilnic pe sprâncene după vindecare, fie ochelari de soare mari, cu protecție UV, pentru eyeliner.
+Trebuie să știi și că, atunci când lucrăm cu alopecia, pielea poate reacționa diferit în funcție de cauza afecțiunii — fie că vorbim de o boală autoimună, un tratament oncologic sau un dezechilibru hormonal. Uneori pigmentul se prinde perfect din prima, alteori avem nevoie de un retuș mai atent pentru a-l fixa uniform. De aceea îmi place să țin legătura cu tine în perioada de vindecare și să ne vedem la control, ca să mă asigur că obținem cel mai bun rezultat posibil.
+Pe scurt, eu vin cu expertiza și atenția la detalii, tu vii cu grija pentru tine în primele săptămâni, și împreună facem ca sprâncenele sau eyelinerul tău să fie exact așa cum ți-ai dorit — frumoase, naturale și de durată.</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134296139/ac5a3c43b5?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MdN1AQsikt4?t=31</t>
+  </si>
+  <si>
+    <t>Dermopigmentarea cosmetică e o procedură fină prin care introduc pigmenți în stratul superficial al pielii, ca să îți armonizez trăsăturile. O mai auzi numită machiaj semi-permanent sau micropigmentare și se face cel mai des pentru sprâncene, buze și eyeliner.
+Pigmenții rămân la suprafață și se estompează treptat, deci în timp ești liberă să schimbi rezultatul. Sunt formulați special pentru față, respectă tonul pielii și dau un aspect natural.
+Tehnica îți pune în valoare frumusețea naturală. Redă forma sprâncenelor, luminează și uniformizează culoarea buzelor, accentuează discret linia genelor.
+Lucrez cu aparatură de ultimă generație și pigmenți de calitate medicală, aleși după tonul pielii. Rezultatul ține între 1 și 3 ani, în funcție de tipul pielii, apoi facem o ședință de reîmprospătare.
+Câștigi timpul de dimineață. Te trezești cu chipul deja gata, te privești în oglindă și te vezi odihnită, exact tu, puțin mai clară.</t>
+  </si>
+  <si>
     <t>sub logo si poza -&gt;</t>
   </si>
   <si>
-    <t>https://youtu.be/IDnRhucH9mI?t=14</t>
-  </si>
-  <si>
     <t>Arta care vindecă</t>
   </si>
   <si>
+    <t>https://vimeo.com/1134274481/532753926d?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
     <t>Un institut unde frumusețea și vindecarea se împletesc natural: dermopigmentare cosmetică pentru naturalețe, dermopigmentare paramedicală pentru echilibru emoțional și training avansat pentru cei ce vor să devină artiști ai empatiei și transformării.</t>
   </si>
   <si>
+    <t>in formularul de programare la pasul 2 - sub alege data</t>
+  </si>
+  <si>
     <t>deasupra de video -&gt; CTA</t>
   </si>
   <si>
@@ -401,13 +425,13 @@
     <t>Numele serviciilor: Areola, Cicatrici, Alopecie, Sprâncene, Eyeliner, Buze</t>
   </si>
   <si>
+    <t>Vrei si alta procedura?</t>
+  </si>
+  <si>
     <t>Pașii transformării tale</t>
   </si>
   <si>
     <t>Consultanță</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134295889/a09ca49b02?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <r>
@@ -486,17 +510,6 @@
     <t>Procedura</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Alopecia, fie ea areată, totală sau cauzată de factori medicali și tratamente precum chimioterapia, aduce cu sine provocări nu doar estetice, ci și practice. Când sprâncenele și genele lipsesc, dermopigmentarea poate reda armonia feței, expresivitatea și încrederea. Dar înainte să ajungem acolo, pregătirea corectă este esențială pentru un rezultat frumos și stabil.
-În primul rând, trebuie să știm cauza alopeciei. Dacă este de natură autoimună sau hormonală (alopecia areată, tiroidită, menopauză), pielea din zonă poate fi mai sensibilă sau cu o capacitate diferită de fixare a pigmentului. Dacă pierderea părului a fost cauzată de tratamente oncologice, este esențial să așteptăm minim 6 luni după încheierea acestora și să avem acordul medicului curant. În cazul alopeciei fără cauză medicală activă, procedura se poate face imediat ce pielea este sănătoasă.
-Hidratarea pielii este crucială, fără fire de păr, pielea sprâncenelor și a pleoapelor tinde să fie mai expusă vântului, soarelui sau frigului, ceea ce o poate usca rapid. În săptămânile de dinainte, folosește o cremă blândă, fără parfum, pentru a menține elasticitatea pielii.
-Evită procedurile agresive în zona ochilor și sprâncenelor cu cel puțin 2 săptămâni înainte: epilare cu ceară, tratamente cu acizi, microdermabraziune sau peelinguri chimice. Acestea pot irita pielea și afecta modul în care pigmentul se fixează.
-În ziua procedurii, evită cafeaua, alcoolul și aspirina sau ibuprofenul, toate pot crește sensibilitatea și riscul de sângerare. Dacă porți lentile de contact, adu și o cutiuță sterilă pentru a le păstra în timpul procedurii eyelinerului.
-În cazul alopeciei, un detaliu foarte important este designul personalizat. Nu desenăm doar o formă de sprânceană „frumoasă” și un eyeliner „plăcut vizual”, lucrăm să reconstruim expresia naturală a feței tale, ținând cont de simetrie, proporții și trăsături. Din acest motiv, în ziua programării îți voi face o simulare completă pe piele, pentru ca tu să vezi și să aprobi rezultatul înainte să începem dermopigmentarea.
-Dacă observ că pielea este iritată, extrem de uscată sau că există inflamații locale, vom reprograma. Nu este amânare, ci o alegere profesională pentru ca rezultatul să fie uniform, stabil și cu adevărat frumos.
-Pregătirea înainte de dermopigmentarea sprâncenelor și eyelinerului în cazul alopeciei este, în esență, o combinație de îngrijire fizică și claritate medicală. Iar eu sunt aici să mă asigur că atunci când ajungi pe patul meu de lucru, atât pielea ta, cât și tu, ca om, sunteți pregătiți pentru o transformare care îți va reda armonia și expresivitatea privirii.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -521,9 +534,6 @@
     </r>
   </si>
   <si>
-    <t>https://youtu.be/XGXztXrRTLc?t=24</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -575,6 +585,9 @@
     <t xml:space="preserve">Întreținere </t>
   </si>
   <si>
+    <t xml:space="preserve">               </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -599,9 +612,6 @@
     </r>
   </si>
   <si>
-    <t>De ce este nevoie de două ședințe?</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -626,16 +636,6 @@
     </r>
   </si>
   <si>
-    <t>https://vimeo.com/1134272378/19b22a3b9a?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
-După prima ședință de dermopigmentare, zona lucrată, fie că vorbim despre sprâncene, buze sau areole, arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
-În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
-Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
-Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -660,9 +660,6 @@
     </r>
   </si>
   <si>
-    <t>https://youtu.be/ovRf93bffLc?t=12</t>
-  </si>
-  <si>
     <t>Programare</t>
   </si>
   <si>
@@ -691,16 +688,6 @@
     <t>bifa anularea programarii</t>
   </si>
   <si>
-    <t>Camuflajul cicatricilor este una dintre acele proceduri care nu schimbă doar aspectul pielii, ci și felul în care te vezi și te simți în propriul corp. Fie că vorbim de cicatrici post-operatorii, de la accident, de la o arsură sau chiar de reconstrucția buzei în urma unui cleft lip, pregătirea corectă înainte de procedură este cheia pentru un rezultat frumos și natural.
-Primul pas este evaluarea cicatricii. Nu toate cicatricile pot fi pigmentate imediat, este esențial să fie complet vindecată. Asta înseamnă, în general, să aibă minim 12 luni vechime, să nu mai fie roșie sau violet, să nu prezinte relief proeminent și să fie stabilă ca textură. Dacă există îndoieli, putem face un test punctual pe o zonă mică pentru a vedea cum reacționează pielea.
-Hidratarea este vitală. O cicatrice uscată sau aspră nu reține pigmentul la fel de uniform. Cu 2-3 săptămâni înainte de procedură, aplică zilnic o cremă sau un ulei blând (cum ar fi cel de migdale dulci sau de jojoba) pentru a ajuta la refacerea elasticității pielii.
-Evită expunerea la soare pe zona respectivă înainte de procedură. O cicatrice bronzată sau arsă solar va avea o nuanță temporară modificată, ceea ce face dificilă alegerea culorii corecte pentru camuflaj.
-Foarte important: dacă urmezi tratamente medicamentoase (cum ar fi corticoizi, imunosupresoare sau anticoagulante), spune-mi din timp. Anumite medicamente pot influența modul în care pielea se vindecă și cât de bine fixează pigmentul.
-În ziua procedurii, pielea trebuie să fie curată și fără produse aplicate, fără creme, uleiuri, fond de ten sau machiaj pe zona respectivă.
-Și poate cel mai important lucru pe care vreau să îl știi: fiecare cicatrice are o poveste și un comportament unic. Din acest motiv, la consultație voi analiza nu doar culoarea și textura pielii tale, ci și factorii care au dus la formarea cicatricii. Asta îmi permite să aleg exact combinația de pigmenți și tehnică potrivită, astfel încât rezultatul să se integreze perfect cu restul pielii.
-Pregătirea înainte de camuflajul cicatricilor nu este complicată, dar fiecare detaliu contează enorm. Eu vin cu experiența și ochiul format, tu vii cu o piele pregătită și împreună facem ca acea cicatrice să treacă neobservată, iar tu să te vezi din nou complet(ă).</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -717,86 +704,10 @@
     </r>
   </si>
   <si>
-    <t>https://youtu.be/vFhzz-YKExI?t=30</t>
-  </si>
-  <si>
     <t>buton Pasul Următor</t>
   </si>
   <si>
     <t>Testimoniale</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134367031/a78e7eed7c?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134392204/bb7f48602f?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Cât rezistă pigmentul?</t>
-  </si>
-  <si>
-    <t>În primele ore, sprâncenele sau eyelinerul vor părea mai intense, mai închise la culoare. Este absolut normal, pigmentul este încă la suprafață și pielea răspunde la procedură. În această fază, îți voi arăta exact cum să cureți delicat zona, astfel încât să îndepărtezi excesul de limfă fără să deranjezi pielea. Foarte important este să nu atingi zona cu mâinile murdare și să eviți complet umezirea directă sau expunerea la căldură și aburi. Piscina, sauna sau dușurile fierbinți nu sunt o opțiune în prima săptămână.
-Pe măsură ce pielea începe să se regenereze, este posibil să apară mici cruste. Știu că tentația de a le desprinde poate fi mare, dar te rog să le lași să cadă singure. Dacă le îndepărtezi înainte de vreme, riști să scoți și pigmentul din piele, lăsând zone fără culoare care nu se pot corecta decât la retuș. Îți voi recomanda un balsam de vindecare special, pe care să îl aplici în strat foarte subțire, cu mâinile curate sau cu un bețișor cosmetic, de câteva ori pe zi.
-În cazul eyelinerului, este normal să simți o ușoară sensibilitate sau să observi o mică umflare a pleoapelor. O simplă compresă rece, aplicată de câteva ori pe zi, ajută enorm la calmarea zonei. La fel de important este să eviți machiajul în jurul ochilor, mascara sau produse uleioase pentru demachiere până când pielea este complet vindecată.
-Protecția solară este un alt pas pe care nu îl poți sări. Chiar și iarna, radiațiile UV pot degrada pigmentul, așa că îți recomand fie un SPF aplicat zilnic pe sprâncene după vindecare, fie ochelari de soare mari, cu protecție UV, pentru eyeliner.
-Trebuie să știi și că, atunci când lucrăm cu alopecia, pielea poate reacționa diferit în funcție de cauza afecțiunii — fie că vorbim de o boală autoimună, un tratament oncologic sau un dezechilibru hormonal. Uneori pigmentul se prinde perfect din prima, alteori avem nevoie de un retuș mai atent pentru a-l fixa uniform. De aceea îmi place să țin legătura cu tine în perioada de vindecare și să ne vedem la control, ca să mă asigur că obținem cel mai bun rezultat posibil.
-Pe scurt, eu vin cu expertiza și atenția la detalii, tu vii cu grija pentru tine în primele săptămâni, și împreună facem ca sprâncenele sau eyelinerul tău să fie exact așa cum ți-ai dorit — frumoase, naturale și de durată.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/MdN1AQsikt4?t=31</t>
-  </si>
-  <si>
-    <t>Dermopigmentarea areolei este, prin natura și scopul ei, o procedură gândită să dureze. Folosim pigmenți organici special concepuți pentru reconstrucția areolei, aleși tocmai pentru stabilitatea lor în timp. Rezultatul? O culoare frumoasă și armonioasă, care își păstrează vitalitatea ani la rând, fără schimbări vizibile sau neplăcute.
-Spre deosebire de alte zone ale corpului, areola nu este expusă constant la soare sau factori care pot grăbi estomparea pigmentului, ceea ce contribuie la o rezistență aproape permanentă. Astfel, o singură procedură corect realizată, urmată de retușul inițial, poate aduce un rezultat de lungă durată, care să nu necesite reîmprospătări frecvente.
-Acesta este și motivul pentru care dermopigmentarea reconstructivă a areolei este considerată o etapă finală, stabilă și sigură în procesul de reconstrucție mamară — o intervenție care oferă liniște, siguranță și o imagine corporală cu care te poți simți din nou împăcată, zi după zi, an după an.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/j8PmKJ4MVAc</t>
-  </si>
-  <si>
-    <t>După ce facem camuflajul unei cicatrici, începe o etapă la fel de importantă ca procedura în sine: perioada de vindecare. Pielea pe care am lucrat a trecut deja printr-un proces de regenerare în trecut, iar acum are nevoie de un pic mai multă răbdare și atenție pentru ca pigmentul să se fixeze frumos și uniform.
-În primele ore, zona camuflată va părea mai intens colorată decât nuanța finală pe care o vom obține. Este normal, pentru că pigmentul este încă la suprafață și pielea reacționează printr-o ușoară roșeață sau umflare. În această fază, este esențial să o cureți delicat, exact cum îți arăt eu, pentru a elimina excesul de limfă și pentru a preveni formarea unor cruste groase.
-În următoarele zile, se vor forma cruste fine, care trebuie lăsate să cadă singure. Știu că tentația de a le atinge este mare, dar dacă le desprinzi, riști să îndepărtezi și pigmentul împreună cu ele, lăsând zone mai deschise la culoare care nu se vor uniformiza decât la ședința de retuș. Aplică balsamul de vindecare pe care ți-l recomand, în strat foarte subțire și doar cu mâinile curate, de câteva ori pe zi.
-Evită apa fierbinte, aburul, piscina, sauna și expunerea directă la soare în primele săptămâni. Căldura și umezeala excesivă pot împiedica fixarea uniformă a pigmentului. După ce zona s-a vindecat complet, protecția solară devine obligatorie, indiferent de sezon, mai ales dacă cicatricea se află pe o zonă expusă, cum ar fi brațele, pieptul sau spatele. Radiațiile UV pot decolora mai repede pigmentul și pot afecta uniformitatea nuanței.
-Un alt aspect important este că fiecare cicatrice are un comportament diferit. Cele mai vechi și stabile se vindecă de obicei mai previzibil, în timp ce cicatricile mai noi, zonele cu piele foarte subțire sau afectate de traumatisme severe pot necesita mai multe ajustări pentru a ajunge la o uniformitate perfectă. Din acest motiv, îmi place să păstrez legătura cu tine pe tot parcursul vindecării, să ne vedem la control și să planificăm împreună eventualele retușuri.
-Pe scurt, eu vin cu tehnica și pigmentul potrivit, tu vii cu răbdarea și îngrijirea zilnică, și împreună transformăm cicatricea ta într-o amintire cât mai discretă, care să nu îți mai atragă atenția de fiecare dată când o vezi.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Gv0ix5mGhV0?t=26</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134274481/532753926d?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134296139/ac5a3c43b5?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134391377/ea32a83a9b?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>in formularul de programare la pasul 2 - sub alege data</t>
-  </si>
-  <si>
-    <t>Vrei si alta procedura?</t>
-  </si>
-  <si>
-    <t>Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
-După prima ședință de dermopigmentare, zona lucrată — fie că vorbim despre sprâncene, buze sau areole — arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
-În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
-Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
-Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imaginează-ți că pielii îi redăm șansa de a se integra armonios, cam asta facem cu camuflajul cicatricilor. În medie, rezultatul poate dura între 3 și 5 ani, uneori chiar mai mult, dacă pielea ta este bine îngrijită și protejată. 
-Durabilitatea depinde foarte mult de câteva elemente cheie: tipul tău de piele, pigmentul folosit, expunerea la soare și bineînțeles modul în care îngrijești zona după procedură. Pielea hidratată, protejată cu SPF și fără produse agresive vor păstra pigmentul vibrant pentru mult timp. 
-La fel ca orice lucrare de finețe, camuflajul cicatricilor vine cu un mic secret: este normal să fie nevoie de retușuri periodice. Nu pentru că ceva nu ar merge bine, ci pentru că pielea își schimbă tonul ușor în timp (da, da și cel mai stabil pigment se luminează puțin), iar viața de zi cu zi ne aduce expunere la soare, chimicale sau uzură normală. Așa că o ședință de întreținere este cea care ajută să păstrăm nuanța perfectă. 
-</t>
-  </si>
-  <si>
-    <t>https://youtu.be/H0CD6xaepQM</t>
   </si>
   <si>
     <t>Când vine vorba de dermopigmentarea sprâncenelor sau a genelor pierdute din cauza alopeciei, rezistența în timp poate fi diferită de la o persoană la alta. În medie, pentru sprâncene vorbim de 1 până la 3 ani, iar pentru eyeliner, deci linia de pigment de la pleoape, de 2 până la 4 ani, pentru că zona ochilor e mai protejată și mai puțin expusă la factori care degradează pigmentul.
@@ -808,28 +719,25 @@
     <t>https://youtu.be/Hu45144u07I</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134392767/81abde8f8b?share=copy&amp;fl=sv&amp;fe=ci</t>
+    <t>pasul 3 - Particularitați</t>
+  </si>
+  <si>
+    <t>Particularități medicale sau ale pielii</t>
+  </si>
+  <si>
+    <t>&lt;- TITLU</t>
+  </si>
+  <si>
+    <t>Pentru siguranța ta și un rezultat optim al procedurii te rugam să ne spui dacă te regăsești în oricare dintre situațiile de mai jos. În unele cazuri procedura poate fi reprogramată până când pielea este complet vindecată sau stabilă.</t>
+  </si>
+  <si>
+    <t>&lt;- TEXT EXPLICATIV</t>
+  </si>
+  <si>
+    <t>ce se intampla daca bifeaza DA</t>
   </si>
   <si>
     <t>https://vimeo.com/1134278521/14da188b87?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>pasul 3 - Particularitați</t>
-  </si>
-  <si>
-    <t>Particularități medicale sau ale pielii</t>
-  </si>
-  <si>
-    <t>&lt;- TITLU</t>
-  </si>
-  <si>
-    <t>Pentru siguranța ta și un rezultat optim al procedurii te rugam să ne spui dacă te regăsești în oricare dintre situațiile de mai jos. În unele cazuri procedura poate fi reprogramată până când pielea este complet vindecată sau stabilă.</t>
-  </si>
-  <si>
-    <t>&lt;- TEXT EXPLICATIV</t>
-  </si>
-  <si>
-    <t>ce se intampla daca bifeaza DA</t>
   </si>
   <si>
     <t>Ati trecut printr-o mastectomie sau altă intervenție chirurgicală în zona sânilor?</t>
@@ -896,6 +804,82 @@
     <t>Există zone întărite, foarte fibroase sau iradiate (piele foarte rigidă) în aria de lucru?</t>
   </si>
   <si>
+    <t>Aveți boli autoimune (ex: Lupus, Hashimoto, vitiligo, psoriazis)?</t>
+  </si>
+  <si>
+    <t>Aveți sistemul imunitar slăbit sau urmați un tratament cu imunosupresoare?</t>
+  </si>
+  <si>
+    <t>Urmați un tratement cu corticosteroizi (pastile, injecții, sau creme aplicate în zona vizată)?</t>
+  </si>
+  <si>
+    <t>Urmați un tratament cu antibiotice în prezent?</t>
+  </si>
+  <si>
+    <t>Aveți alergii severe (anestezici, pigmenți, latex, metale, altele)?</t>
+  </si>
+  <si>
+    <t>daca biseaza DA trebuie casuta pentru a putea scrie la ce</t>
+  </si>
+  <si>
+    <t>Aveți diabet?</t>
+  </si>
+  <si>
+    <t>Camuflajul cicatricilor prin dermopigmentare paramedicală</t>
+  </si>
+  <si>
+    <t>Suferiți de tulburări de coagulare sau urmați un tratament anticoagulant?</t>
+  </si>
+  <si>
+    <t>Ati facut recent tratamente în zona pieptului ( laser, peeling-uri, microneedling, PRP)?</t>
+  </si>
+  <si>
+    <t>Ati facut injecții cu corticosteroizi in cicatrici?</t>
+  </si>
+  <si>
+    <t>Descoperă cum fiecare nuanță atent aleasă poate estompa cu blândețe urmele trecutului.</t>
+  </si>
+  <si>
+    <t>Daca nu esti sigură, scrie-ne in câteva cuvinte situația ta și vom face online o evaluare personalizată</t>
+  </si>
+  <si>
+    <t>trebuie casuta pentru a putea scrie la ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ți-am pregătit cele mai importante întrebări și răspunsuri despre camuflarea cicatricilor, explicate clar, atât în text, cât și în video, ca să știi exact la ce să te aștepți de la această procedură.</t>
+  </si>
+  <si>
+    <t>Ce este camuflajul cicatricilor prin dermopigmentare?</t>
+  </si>
+  <si>
+    <t>Fiecare cicatrice are o poveste. Unele vorbesc despre vindecare, altele despre accidente sau intervenții care ți-au schimbat viața. Dar indiferent de cum au apărut: după o operație, o rană, un accident, o arsură sau chiar din naștere, cum este cazul cleft lip (buza despărțită), toate pot aduce cu ele amintiri pe care poate nu îți dorești să le vezi zilnic în oglindă.
+Camuflajul cicatricilor prin dermopigmentare este o tehnică specializată prin care uniformizez culoarea pielii din zona cicatricii, pentru ca aceasta să se integreze cât mai natural cu pielea din jur. Folosesc un dermograf profesional și pigmenți medicali, formulați pentru a se adapta tonului tău de piele, astfel încât rezultatul să fie discret și armonios.
+Procedura poate fi aplicată pentru cicatrici plate și vindecate complet, inclusiv pentru cele rezultate din intervenții chirurgicale, cezariană, reconstrucții, răni, accidente, arsuri, dar și pentru cicatricile rezultate din cleft lip. În acest tip de lucrări, precizia tehnică se îmbină cu o evaluare atentă a nuanțelor pielii, pentru a obține un efect cât mai natural.
+Înainte de a începe, discutăm despre istoricul cicatricii, despre așteptări și despre ce este realist să obținem, pentru că fiecare tip de piele reacționează diferit. Lucrez cu răbdare și în pași mici, pentru a respecta integritatea pielii și a obține un rezultat durabil și plăcut vizual.
+Rezultatul final? O piele cu un aspect mai uniform, în care cicatricea devine mult mai puțin vizibilă, iar tu poți să îți privești corpul cu mai multă liniște și încredere.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HubjqYkzxww?t=29</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134390484/703fcfc3bf?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>ce fel de pigmenti folosesc?</t>
+  </si>
+  <si>
+    <t>Când lucram pe cicatrici, e vorba de a acoperi o zonă, dar si  de a o integra perfect în restul pielii, astfel încât să nu mai atragă atenția. Asta înseamnă că pigmentul trebuie ales cu o precizie extremă, atât ca nuanță, cât și ca formulă.
+Folosesc pigmenți special concepuți pentru camuflaj paramedical, hipoalergenici, fără metale grele, formulați pentru a fi biocompatibili cu pielea umană. Acești pigmenți nu sunt culori simple dintr-o cutie: îi combin personalizat, în funcție de tonul și subtonul pielii tale, dar și de particularitățile cicatricii.
+Pentru cicatricile mai vechi și complet vindecate, formula pigmentului poate fi mai bogată în tonuri calde sau reci, pentru a contrabalansa nuanța pe care o are cicatricea în mod natural. În cazul cicatricilor rezultate din intervenții chirurgicale, accidente sau afecțiuni precum despicătura de buză (cleft lip), mă asigur că pigmentul ales rămâne stabil și se estompează uniform, fără să capete tonuri nedorite în timp.
+Rezistența culorii poate fi influențată și de textura cicatricii, zonele mai fibroase pot reține diferit pigmentul,  motiv pentru care ajustez concentrația și tehnica de implantare. Toate aceste detalii fac parte dintr-un proces atent, în care scopul meu e să creez o armonie vizuală care să îți redea încrederea în tine.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sUWovJxULxo?t=11</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134390997/593494e586?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
     <t>decriere raspuns din video</t>
   </si>
   <si>
@@ -905,22 +889,13 @@
     <t>Descoperă cum o procedură delicată aduce simetria și naturalețea sprâncenelor tale.</t>
   </si>
   <si>
-    <t>Aveți boli autoimune (ex: Lupus, Hashimoto, vitiligo, psoriazis)?</t>
-  </si>
-  <si>
     <t>Aici găsești explicațiile de care ai nevoie pentru a înțelege cum funcționează dermopigmentarea sprâncenelor și ce rezultate poți obține. Am răspuns la tot ce te frământă, ca să înțelegi procesul și să te simți în siguranță.</t>
   </si>
   <si>
     <t>Ce este dermopigmentarea sprâncenelor?</t>
   </si>
   <si>
-    <t>Aveți sistemul imunitar slăbit sau urmați un tratament cu imunosupresoare?</t>
-  </si>
-  <si>
-    <t>Urmați un tratement cu corticosteroizi (pastile, injecții, sau creme aplicate în zona vizată)?</t>
-  </si>
-  <si>
-    <t>Urmați un tratament cu antibiotice în prezent?</t>
+    <t>Procedura e dureroasa?</t>
   </si>
   <si>
     <t>Sprâncenele sunt una dintre cele mai importante trăsături ale feței. Ele îți definesc expresia, îți încadrează privirea și pot schimba complet armonia chipului. Dermopigmentarea sprâncenelor este metoda prin care putem reda forma, densitatea și echilibrul estetic al sprâncenelor, folosind culoare adaptată natural pielii și trăsăturilor tale.
@@ -934,31 +909,7 @@
     <t>https://youtu.be/SSxSD0cCk6U</t>
   </si>
   <si>
-    <t>Aveți alergii severe (anestezici, pigmenți, latex, metale, altele)?</t>
-  </si>
-  <si>
-    <t>daca biseaza DA trebuie casuta pentru a putea scrie la ce</t>
-  </si>
-  <si>
-    <t>Aveți diabet?</t>
-  </si>
-  <si>
-    <t>Suferiți de tulburări de coagulare sau urmați un tratament anticoagulant?</t>
-  </si>
-  <si>
-    <t>Ati facut recent tratamente în zona pieptului ( laser, peeling-uri, microneedling, PRP)?</t>
-  </si>
-  <si>
-    <t>Ati facut injecții cu corticosteroizi in cicatrici?</t>
-  </si>
-  <si>
     <t>https://vimeo.com/1134367784/47a9bbbeb3?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Daca nu esti sigură, scrie-ne in câteva cuvinte situația ta și vom face online o evaluare personalizată</t>
-  </si>
-  <si>
-    <t>trebuie casuta pentru a putea scrie la ce</t>
   </si>
   <si>
     <t>Microblading vs Dermopigmentare fir cu fir?</t>
@@ -987,7 +938,32 @@
     <t>https://youtu.be/fCed8uYGo-4?t=6</t>
   </si>
   <si>
+    <t>descriere raspuns</t>
+  </si>
+  <si>
+    <t>Privire definită prin dermopigmentarea eyelinerului</t>
+  </si>
+  <si>
     <t>https://vimeo.com/1134368477/8ba79470df?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Descoperă cum dermopigmentarea eyelinerului poate da profunzime privirii tale printr-o eleganță zilnică</t>
+  </si>
+  <si>
+    <t>Întrebările tale sunt firești. Răspunsurile mele sunt aici ca să te ghideze și să-ți arate cât de sigură și delicată este procedura.</t>
+  </si>
+  <si>
+    <t>Ce este dermopigmentarea eyelinerului?</t>
+  </si>
+  <si>
+    <t>Privirea spune întotdeauna o poveste, iar linia fină de la baza genelor poate schimba subtil expresia ochilor și felul în care te percepi în oglindă. Dermopigmentarea eyelinerului este o tehnică prin care evidențiez și definesc linia genelor, pentru a crea un efect de ochi mai expresivi și mai luminoși, fără să fie nevoie de machiaj zilnic.
+Este o alegere ideală dacă îți dorești să economisești timp dimineața, să nu te mai preocupe tușul care se întinde sau dispare pe parcursul zilei, sau dacă ai ochii sensibili și vrei să eviți produsele cosmetice aplicate zilnic.
+Procedura se realizează cu un dermograf profesional și pigmenți speciali, introduși foarte fin la baza genelor. În funcție de preferințele tale, linia poate fi extrem de discretă, doar pentru a accentua privirea, sau puțin mai pronunțată, pentru un efect asemănător unui machiaj perfect trasat.
+Dermopigmentarea eyelinerului nu încarcă ochii, nu creează un aspect artificial și este personalizată în funcție de forma ochilor, de culoarea irisului și de stilul tău de viață. Rezultatul poate dura între 2 și 5 ani, estompându-se natural în timp, iar intensitatea poate fi reîmprospătată atunci când îți dorești.
+Rezultatul final? Un contur fin, armonios și expresiv, care îți luminează privirea și îți oferă siguranța că ochii tăi arată impecabil în orice moment al zilei, fără efort.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1aeMEdsXmQY</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1003,6 +979,25 @@
 Pe scurt: nu este complet lipsită de senzații, dar este o procedură gândită să fie blândă, sigură și suportabilă, astfel încât experiența ta să fie cât mai relaxată și lipsită de stres.</t>
   </si>
   <si>
+    <t>https://vimeo.com/1134394187/722534b82b?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Camuflajul cicatricilor este una dintre acele proceduri care nu schimbă doar aspectul pielii, ci și felul în care te vezi și te simți în propriul corp. Fie că vorbim de cicatrici post-operatorii, de la accident, de la o arsură sau chiar de reconstrucția buzei în urma unui cleft lip, pregătirea corectă înainte de procedură este cheia pentru un rezultat frumos și natural.
+Primul pas este evaluarea cicatricii. Nu toate cicatricile pot fi pigmentate imediat, este esențial să fie complet vindecată. Asta înseamnă, în general, să aibă minim 12 luni vechime, să nu mai fie roșie sau violet, să nu prezinte relief proeminent și să fie stabilă ca textură. Dacă există îndoieli, putem face un test punctual pe o zonă mică pentru a vedea cum reacționează pielea.
+Hidratarea este vitală. O cicatrice uscată sau aspră nu reține pigmentul la fel de uniform. Cu 2-3 săptămâni înainte de procedură, aplică zilnic o cremă sau un ulei blând (cum ar fi cel de migdale dulci sau de jojoba) pentru a ajuta la refacerea elasticității pielii.
+Evită expunerea la soare pe zona respectivă înainte de procedură. O cicatrice bronzată sau arsă solar va avea o nuanță temporară modificată, ceea ce face dificilă alegerea culorii corecte pentru camuflaj.
+Foarte important: dacă urmezi tratamente medicamentoase (cum ar fi corticoizi, imunosupresoare sau anticoagulante), spune-mi din timp. Anumite medicamente pot influența modul în care pielea se vindecă și cât de bine fixează pigmentul.
+În ziua procedurii, pielea trebuie să fie curată și fără produse aplicate, fără creme, uleiuri, fond de ten sau machiaj pe zona respectivă.
+Și poate cel mai important lucru pe care vreau să îl știi: fiecare cicatrice are o poveste și un comportament unic. Din acest motiv, la consultație voi analiza nu doar culoarea și textura pielii tale, ci și factorii care au dus la formarea cicatricii. Asta îmi permite să aleg exact combinația de pigmenți și tehnică potrivită, astfel încât rezultatul să se integreze perfect cu restul pielii.
+Pregătirea înainte de camuflajul cicatricilor nu este complicată, dar fiecare detaliu contează enorm. Eu vin cu experiența și ochiul format, tu vii cu o piele pregătită și împreună facem ca acea cicatrice să treacă neobservată, iar tu să te vezi din nou complet(ă).</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vFhzz-YKExI?t=30</t>
+  </si>
+  <si>
+    <t>Ce fel de pigmenti folosesc?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Este una dintre întrebările pe care le primesc cel mai des, și vreau să îți răspund sincer și complet. În teorie, dermopigmentarea cosmetică acționează doar în straturile superficiale ale pielii, folosind pigmenți biocompatibili și anestezice locale aplicate pe suprafață. Lucrez cu consumabile sterile, de unică folosință, într-un mediu care respectă toate normele de igienă și siguranță.
 Cu toate acestea, conform recomandărilor de bune practici, toate procedurile estetice, inclusiv dermopigmentarea, sunt contraindicate în perioada sarcinii și alăptării. Motivul? Principiul de precauție. Chiar dacă riscul de reacții adverse este redus, corpul trece prin schimbări hormonale și fiziologice importante, iar orice stres suplimentar sau reacție locală poate influența starea ta generală și, indirect, alăptarea.
@@ -1010,7 +1005,34 @@
 Siguranța și sănătatea ta sunt mereu pe primul loc. Dermopigmentarea este despre frumusețe, dar mai ales despre grijă, responsabilitate și respect pentru corpul tău.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+Pentru mine, eyelinerul nu este doar o linie trasată pe pleoapă. Este acel detaliu care îți schimbă întreaga expresie a privirii și care trebuie să rămână frumos și clar ani de zile. Iar totul începe cu pigmentul.
+Lucrez doar cu pigmenți cosmetici premium, creați special pentru zona sensibilă a ochilor, biocompatibili și hipoalergenici. Asta înseamnă că pielea îi acceptă ușor, fără iritații și fără riscul ca, în timp, culoarea să își schimbe nuanța în albastru, verde sau gri. Aleg mereu nuanțe pure, cu o formulă stabilă, astfel încât linia să își păstreze intensitatea fără să se estompeze inestetic.
+Înainte să aleg pigmentul final, îți analizez tonul pielii, culoarea ochilor și efectul pe care ți-l dorești: fie că vrei o privire intensă, de tip cat-eye, fie un efect mai discret și natural. Pigmentul nu este doar „negru sau maro”, este adaptat special pentru tine, astfel încât eyelinerul să îți pună în valoare frumusețea, nu să o înăsprească.
+Folosesc formule cu densitate optimă, care se așază uniform în piele, fără să migreze și fără să piardă claritatea în timp. Rezultatul? Un eyeliner care îți va complimenta privirea zi de zi, fără să ai grija retușurilor frecvente.</t>
+  </si>
+  <si>
     <t>https://youtu.be/UCzGcLsOzk0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/q-gNZ08jBuE?t=18</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134392204/bb7f48602f?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134395372/5172d4ad3b?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>După ce facem camuflajul unei cicatrici, începe o etapă la fel de importantă ca procedura în sine: perioada de vindecare. Pielea pe care am lucrat a trecut deja printr-un proces de regenerare în trecut, iar acum are nevoie de un pic mai multă răbdare și atenție pentru ca pigmentul să se fixeze frumos și uniform.
+În primele ore, zona camuflată va părea mai intens colorată decât nuanța finală pe care o vom obține. Este normal, pentru că pigmentul este încă la suprafață și pielea reacționează printr-o ușoară roșeață sau umflare. În această fază, este esențial să o cureți delicat, exact cum îți arăt eu, pentru a elimina excesul de limfă și pentru a preveni formarea unor cruste groase.
+În următoarele zile, se vor forma cruste fine, care trebuie lăsate să cadă singure. Știu că tentația de a le atinge este mare, dar dacă le desprinzi, riști să îndepărtezi și pigmentul împreună cu ele, lăsând zone mai deschise la culoare care nu se vor uniformiza decât la ședința de retuș. Aplică balsamul de vindecare pe care ți-l recomand, în strat foarte subțire și doar cu mâinile curate, de câteva ori pe zi.
+Evită apa fierbinte, aburul, piscina, sauna și expunerea directă la soare în primele săptămâni. Căldura și umezeala excesivă pot împiedica fixarea uniformă a pigmentului. După ce zona s-a vindecat complet, protecția solară devine obligatorie, indiferent de sezon, mai ales dacă cicatricea se află pe o zonă expusă, cum ar fi brațele, pieptul sau spatele. Radiațiile UV pot decolora mai repede pigmentul și pot afecta uniformitatea nuanței.
+Un alt aspect important este că fiecare cicatrice are un comportament diferit. Cele mai vechi și stabile se vindecă de obicei mai previzibil, în timp ce cicatricile mai noi, zonele cu piele foarte subțire sau afectate de traumatisme severe pot necesita mai multe ajustări pentru a ajunge la o uniformitate perfectă. Din acest motiv, îmi place să păstrez legătura cu tine pe tot parcursul vindecării, să ne vedem la control și să planificăm împreună eventualele retușuri.
+Pe scurt, eu vin cu tehnica și pigmentul potrivit, tu vii cu răbdarea și îngrijirea zilnică, și împreună transformăm cicatricea ta într-o amintire cât mai discretă, care să nu îți mai atragă atenția de fiecare dată când o vezi.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Gv0ix5mGhV0?t=26</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1026,7 +1048,17 @@
     <t>https://youtu.be/YRoTT317e6c</t>
   </si>
   <si>
+    <t>https://vimeo.com/1134391377/ea32a83a9b?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
     <t>https://vimeo.com/1134367985/5b6e8713e0?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
+După prima ședință de dermopigmentare, zona lucrată — fie că vorbim despre sprâncene, buze sau areole — arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
+În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
+Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
+Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
   </si>
   <si>
     <t>După dermopigmentarea sprâncenelor, felul în care ai grijă de ele în primele zile este absolut esențial pentru cât de frumos și uniform se va fixa pigmentul. Primele 7-10 zile sunt perioada în care pielea se vindecă, iar ceea ce faci sau nu faci acum poate face diferența între un rezultat impecabil și unul cu mici goluri de culoare.
@@ -1037,74 +1069,6 @@
   </si>
   <si>
     <t>https://youtu.be/04nx2UeEPrk</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134367377/6cc098459a?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
-După prima ședință de dermopigmentare, zona lucrată, fie că vorbim despre sprâncene, buze sau areole,  arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
-În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
-Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
-Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
-  </si>
-  <si>
-    <t>descriere raspuns</t>
-  </si>
-  <si>
-    <t>Privire definită prin dermopigmentarea eyelinerului</t>
-  </si>
-  <si>
-    <t>Descoperă cum dermopigmentarea eyelinerului poate da profunzime privirii tale printr-o eleganță zilnică</t>
-  </si>
-  <si>
-    <t>Întrebările tale sunt firești. Răspunsurile mele sunt aici ca să te ghideze și să-ți arate cât de sigură și delicată este procedura.</t>
-  </si>
-  <si>
-    <t>Ce este dermopigmentarea eyelinerului?</t>
-  </si>
-  <si>
-    <t>Durata rezultatelor variază, dar în general te poți bucura de sprâncene frumoase între 1 și 3 ani. Diferența depinde de mai mulți factori: tipul de piele, nuanța pigmentului ales, stilul de viață și, mai ales, îngrijirea după procedură.
-În primele săptămâni, sprâncenele trec printr-un proces natural de vindecare: culoarea se deschide treptat și se așază uniform. Pentru a păstra rezultatul cât mai mult, este important să lași pielea să se refacă în ritmul ei, să nu desprinzi crustele și să protejezi zona de soare folosind mereu un SPF ridicat.
-Pe termen lung, există factori care pot accelera estomparea pigmentului, de exemplu: produsele cu vitamina C, retinoizi sau acizi exfolianți, expunerea frecventă la apă cu clor sau solarul. Și nuanțele mai deschise, precum blondul sau șatenul deschis, tind să își piardă intensitatea mai repede decât cele mai închise.
-Pentru a menține forma clară și culoarea vibrantă, recomand retușuri de întreținere ori de câte ori simți că sprâncenele au nevoie de un refresh.
-În esență, eu pun bazele unui rezultat de durată, iar tu, prin îngrijirea zilnică, îl păstrezi frumos pentru cât mai mult timp.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/E3GI-l7Ww8s</t>
-  </si>
-  <si>
-    <t>Privirea spune întotdeauna o poveste, iar linia fină de la baza genelor poate schimba subtil expresia ochilor și felul în care te percepi în oglindă. Dermopigmentarea eyelinerului este o tehnică prin care evidențiez și definesc linia genelor, pentru a crea un efect de ochi mai expresivi și mai luminoși, fără să fie nevoie de machiaj zilnic.
-Este o alegere ideală dacă îți dorești să economisești timp dimineața, să nu te mai preocupe tușul care se întinde sau dispare pe parcursul zilei, sau dacă ai ochii sensibili și vrei să eviți produsele cosmetice aplicate zilnic.
-Procedura se realizează cu un dermograf profesional și pigmenți speciali, introduși foarte fin la baza genelor. În funcție de preferințele tale, linia poate fi extrem de discretă, doar pentru a accentua privirea, sau puțin mai pronunțată, pentru un efect asemănător unui machiaj perfect trasat.
-Dermopigmentarea eyelinerului nu încarcă ochii, nu creează un aspect artificial și este personalizată în funcție de forma ochilor, de culoarea irisului și de stilul tău de viață. Rezultatul poate dura între 2 și 5 ani, estompându-se natural în timp, iar intensitatea poate fi reîmprospătată atunci când îți dorești.
-Rezultatul final? Un contur fin, armonios și expresiv, care îți luminează privirea și îți oferă siguranța că ochii tăi arată impecabil în orice moment al zilei, fără efort.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/1aeMEdsXmQY</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134368590/75f90c8f95?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134394187/722534b82b?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>Ce fel de pigmenti folosesc?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Pentru mine, eyelinerul nu este doar o linie trasată pe pleoapă. Este acel detaliu care îți schimbă întreaga expresie a privirii și care trebuie să rămână frumos și clar ani de zile. Iar totul începe cu pigmentul.
-Lucrez doar cu pigmenți cosmetici premium, creați special pentru zona sensibilă a ochilor, biocompatibili și hipoalergenici. Asta înseamnă că pielea îi acceptă ușor, fără iritații și fără riscul ca, în timp, culoarea să își schimbe nuanța în albastru, verde sau gri. Aleg mereu nuanțe pure, cu o formulă stabilă, astfel încât linia să își păstreze intensitatea fără să se estompeze inestetic.
-Înainte să aleg pigmentul final, îți analizez tonul pielii, culoarea ochilor și efectul pe care ți-l dorești: fie că vrei o privire intensă, de tip cat-eye, fie un efect mai discret și natural. Pigmentul nu este doar „negru sau maro”, este adaptat special pentru tine, astfel încât eyelinerul să îți pună în valoare frumusețea, nu să o înăsprească.
-Folosesc formule cu densitate optimă, care se așază uniform în piele, fără să migreze și fără să piardă claritatea în timp. Rezultatul? Un eyeliner care îți va complimenta privirea zi de zi, fără să ai grija retușurilor frecvente.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/q-gNZ08jBuE?t=18</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134395372/5172d4ad3b?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1118,22 +1082,36 @@
 Așa că pregătirea este, de fapt, primul pas din procedura ta. Tu vii cu ochii curați și odihniți, eu vin cu expertiza și precizia, iar împreună facem ca privirea ta să capete acel contur elegant și luminos care te va pune în valoare ani de zile.</t>
   </si>
   <si>
+    <t>https://vimeo.com/1134367377/6cc098459a?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
     <t>https://youtu.be/MHHjA0l00X8</t>
   </si>
   <si>
     <t>https://vimeo.com/1134394572/406e5f7801?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>link raspuns</t>
+    <t xml:space="preserve">Imaginează-ți că pielii îi redăm șansa de a se integra armonios, cam asta facem cu camuflajul cicatricilor. În medie, rezultatul poate dura între 3 și 5 ani, uneori chiar mai mult, dacă pielea ta este bine îngrijită și protejată. 
+Durabilitatea depinde foarte mult de câteva elemente cheie: tipul tău de piele, pigmentul folosit, expunerea la soare și bineînțeles modul în care îngrijești zona după procedură. Pielea hidratată, protejată cu SPF și fără produse agresive vor păstra pigmentul vibrant pentru mult timp. 
+La fel ca orice lucrare de finețe, camuflajul cicatricilor vine cu un mic secret: este normal să fie nevoie de retușuri periodice. Nu pentru că ceva nu ar merge bine, ci pentru că pielea își schimbă tonul ușor în timp (da, da și cel mai stabil pigment se luminează puțin), iar viața de zi cu zi ne aduce expunere la soare, chimicale sau uzură normală. Așa că o ședință de întreținere este cea care ajută să păstrăm nuanța perfectă. 
+</t>
+  </si>
+  <si>
+    <t>https://youtu.be/H0CD6xaepQM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Este o întrebare pe care o primesc foarte des și e firesc să o ai și tu în minte. Răspunsul scurt este: pentru că fiecare piele este unică și reacționează diferit la pigment.
+După prima ședință de dermopigmentare, zona lucrată, fie că vorbim despre sprâncene, buze sau areole,  arată mai intensă. Pigmentul este proaspăt depus, iar pielea este ușor inflamată. În următoarele săptămâni, în timpul procesului natural de vindecare, culoarea începe să se estompeze și să se așeze, până ajunge la nuanța finală.
+În această perioadă, pielea elimină în mod natural un procent din pigment. Este reacția normală a organismului la orice element introdus din exterior. Și aici intervine retușul: este a doua ședință în care completăm zonele unde pigmentul s-a fixat mai puțin, uniformizăm culoarea, ajustăm simetria dacă e nevoie și întărim contururile.
+Retușul este esențial pentru un rezultat uniform, de lungă durată și cu aspect natural. După ce pielea s-a „obișnuit” cu pigmentul la prima procedură, îl va accepta mult mai bine la a doua, ceea ce face ca rezultatul final să fie stabil și frumos în timp.
+Pe scurt: prima procedură pregătește terenul, iar retușul finalizează lucrarea. Fără retuș, rezultatul este doar pe jumătate. Cu retuș, ai sprâncene, buze sau areole așa cum ți le dorești, pentru mai mult timp și fără surprize.</t>
   </si>
   <si>
     <t>Ce se întâmplă imediat dupa și cum întrețin procedura?</t>
   </si>
   <si>
-    <t>Zâmbet definit prin dermopigmentare buzelor</t>
-  </si>
-  <si>
-    <t>Descopera cum dermopigmentare buzelor poate adăuga profunzime si senzualitate zâmbetului tau</t>
+    <t>https://vimeo.com/1134392767/81abde8f8b?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t>După ce ai făcut dermopigmentarea eyelinerului, începe perioada în care ochii tăi au nevoie de un pic de răsfăț și atenție în plus. Nu e nimic complicat, dar fiecare detaliu contează ca rezultatul să rămână frumos, clar și uniform ani la rând.
@@ -1148,6 +1126,43 @@
     <t>https://youtu.be/Wa8FwhbD5e4</t>
   </si>
   <si>
+    <t>https://vimeo.com/1134393651/6595a65058?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Durata rezultatelor variază, dar în general te poți bucura de sprâncene frumoase între 1 și 3 ani. Diferența depinde de mai mulți factori: tipul de piele, nuanța pigmentului ales, stilul de viață și, mai ales, îngrijirea după procedură.
+În primele săptămâni, sprâncenele trec printr-un proces natural de vindecare: culoarea se deschide treptat și se așază uniform. Pentru a păstra rezultatul cât mai mult, este important să lași pielea să se refacă în ritmul ei, să nu desprinzi crustele și să protejezi zona de soare folosind mereu un SPF ridicat.
+Pe termen lung, există factori care pot accelera estomparea pigmentului, de exemplu: produsele cu vitamina C, retinoizi sau acizi exfolianți, expunerea frecventă la apă cu clor sau solarul. Și nuanțele mai deschise, precum blondul sau șatenul deschis, tind să își piardă intensitatea mai repede decât cele mai închise.
+Pentru a menține forma clară și culoarea vibrantă, recomand retușuri de întreținere ori de câte ori simți că sprâncenele au nevoie de un refresh.
+În esență, eu pun bazele unui rezultat de durată, iar tu, prin îngrijirea zilnică, îl păstrezi frumos pentru cât mai mult timp.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/E3GI-l7Ww8s</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134368590/75f90c8f95?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Eyelinerul obținut prin dermopigmentare este una dintre procedurile cu cea mai lungă durată de viață, în medie între 2 și 4 ani, uneori chiar mai mult. Acest lucru se datorează atât zonei delicate în care lucrăm, cât și faptului că pielea pleoapelor este protejată de soare, de produse exfoliante și de frecarea zilnică la care sunt expuse alte zone ale feței.
+Procesul de estompare este mult mai lent decât în cazul sprâncenelor. Pigmentul rămâne mai stabil, iar linia păstrează claritatea mai mult timp. Totuși, durata exactă depinde de factori precum tipul de piele, intensitatea culorii alese, metabolismul individual și sensibilitatea pielii din zona ochilor.
+Îngrijirea corectă imediat după procedură joacă un rol important: evitarea machiajului pe pleoape în perioada de vindecare, protejarea zonei de apă sărată sau cu clor și respectarea tuturor recomandărilor de igienă vor ajuta pigmentul să se fixeze optim.
+Chiar dacă eyelinerul dermopigmentat se menține mai mult decât alte zone, retușurile de întreținere sunt recomandate atunci când îți dorești să intensifici din nou culoarea sau să ajustezi forma, astfel încât să te bucuri de privirea conturată perfect ani la rând.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uDqRY-0acYc</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134395673/68f4090c6f?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>link raspuns</t>
+  </si>
+  <si>
+    <t>Zâmbet definit prin dermopigmentare buzelor</t>
+  </si>
+  <si>
+    <t>Descopera cum dermopigmentare buzelor poate adăuga profunzime si senzualitate zâmbetului tau</t>
+  </si>
+  <si>
     <t>Ți-am pregătit cele mai importante întrebări și răspunsuri despre dermopigmentare buzelor, explicate clar, atât în text, cât și în video, ca să știi exact la ce să te aștepți de la această procedură.</t>
   </si>
   <si>
@@ -1159,9 +1174,6 @@
 Procedura se realizează cu ajutorul unui dermograf profesional și pigmenți speciali, aleși în nuanțe care să se potrivească tonului pielii și să complimenteze trăsăturile tale. Rezultatul final poate fi foarte discret, pentru un efect natural „my lips but better”, sau mai intens, în funcție de dorințele tale.
 Dermopigmentarea buzelor nu înseamnă o culoare puternică și rigidă, ci o nuanță transparentă, caldă, care se integrează perfect în textura pielii buzelor. Pigmentul se estompează treptat în timp, ceea ce îți permite să ajustezi sau să reîmprospătezi culoarea ori de câte ori simți nevoia.
 Rezultatul final? Buze cu un contur mai definit, o culoare uniformă și un aspect sănătos, care îți vor face zâmbetul să iasă în evidență în cel mai frumos mod, în fiecare zi, fără efort.</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1134393651/6595a65058?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t>https://youtu.be/XRCC39PFXdM</t>
@@ -1181,25 +1193,10 @@
     <t>https://youtu.be/CkYW5nyM3eo</t>
   </si>
   <si>
-    <t>Eyelinerul obținut prin dermopigmentare este una dintre procedurile cu cea mai lungă durată de viață, în medie între 2 și 4 ani, uneori chiar mai mult. Acest lucru se datorează atât zonei delicate în care lucrăm, cât și faptului că pielea pleoapelor este protejată de soare, de produse exfoliante și de frecarea zilnică la care sunt expuse alte zone ale feței.
-Procesul de estompare este mult mai lent decât în cazul sprâncenelor. Pigmentul rămâne mai stabil, iar linia păstrează claritatea mai mult timp. Totuși, durata exactă depinde de factori precum tipul de piele, intensitatea culorii alese, metabolismul individual și sensibilitatea pielii din zona ochilor.
-Îngrijirea corectă imediat după procedură joacă un rol important: evitarea machiajului pe pleoape în perioada de vindecare, protejarea zonei de apă sărată sau cu clor și respectarea tuturor recomandărilor de igienă vor ajuta pigmentul să se fixeze optim.
-Chiar dacă eyelinerul dermopigmentat se menține mai mult decât alte zone, retușurile de întreținere sunt recomandate atunci când îți dorești să intensifici din nou culoarea sau să ajustezi forma, astfel încât să te bucuri de privirea conturată perfect ani la rând.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/uDqRY-0acYc</t>
-  </si>
-  <si>
     <t>https://vimeo.com/1134389220/8415256c6d?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134395673/68f4090c6f?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
     <t>E procedura dureroasă?</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=R0d-AAGRoPk</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1215,9 +1212,6 @@
     <t>https://vimeo.com/1134388877/d988818871?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134406208/b61dd3b03b?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
     <t>"După ce ai făcut dermopigmentarea buzelor, începe perioada de vindecare, care e la fel de importantă ca procedura în sine pentru a obține un rezultat frumos și uniform.
 În primele ore, buzele pot părea mai intense ca nuanță decât ți-ai imaginat, iar acest lucru este perfect normal. Pigmentul este încă la suprafață, iar în următoarele zile, culoarea se va estompa treptat, ajungând la nuanța finală. În acest timp, poți simți și o ușoară senzație de tensiune sau uscăciune.
 Foarte important: buzele nu trebuie frecate, zgâriate sau atinse cu mâinile murdare. Dacă apar cruste fine, lasă-le să cadă singure. Îndepărtarea lor forțată poate scoate și pigmentul odată cu ele, lăsând zone mai deschise.
@@ -1231,13 +1225,13 @@
     <t>https://youtu.be/N7b-HzakFSo</t>
   </si>
   <si>
-    <t>https://youtu.be/316Jks2ngjw</t>
-  </si>
-  <si>
     <t>https://vimeo.com/1134388372/1908b861f6?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
-    <t>https://vimeo.com/1134405752/6c788c73f7?share=copy&amp;fl=sv&amp;fe=ci</t>
+    <t>https://www.youtube.com/watch?v=R0d-AAGRoPk</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134406208/b61dd3b03b?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1251,6 +1245,12 @@
   </si>
   <si>
     <t>https://vimeo.com/1134389434/e883b4d0ad?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://youtu.be/316Jks2ngjw</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1134405752/6c788c73f7?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <r>
@@ -1335,6 +1335,10 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1348,10 +1352,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <color rgb="FF980000"/>
@@ -1398,10 +1398,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1413,14 +1413,14 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1701,188 +1701,188 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="C5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="2" t="s">
         <v>81</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="7"/>
+        <v>92</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="10"/>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
@@ -1892,36 +1892,36 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2013,155 +2013,155 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1"/>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>82</v>
+        <v>53</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>99</v>
+        <v>66</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -2265,7 +2265,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="13" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
@@ -2454,13 +2454,13 @@
     </row>
     <row r="102">
       <c r="A102" s="11" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -2469,10 +2469,10 @@
     <row r="103">
       <c r="A103" s="14"/>
       <c r="B103" s="11" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D103" s="14"/>
       <c r="E103" s="14"/>
@@ -2485,217 +2485,217 @@
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
       <c r="F104" s="11" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11"/>
       <c r="B105" s="11" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11"/>
       <c r="B106" s="11" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
       <c r="E106" s="14"/>
       <c r="F106" s="11" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14"/>
       <c r="B107" s="11" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14"/>
       <c r="B108" s="11" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="11" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14"/>
       <c r="B109" s="11" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
       <c r="E109" s="16"/>
       <c r="F109" s="11" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14"/>
       <c r="B110" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
       <c r="E110" s="16"/>
       <c r="F110" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14"/>
       <c r="B111" s="11" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
       <c r="E111" s="16"/>
       <c r="F111" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14"/>
       <c r="B112" s="11" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
       <c r="E112" s="16"/>
       <c r="F112" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14"/>
       <c r="B113" s="11" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
       <c r="E113" s="16"/>
       <c r="F113" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14"/>
       <c r="B114" s="11" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
       <c r="E114" s="16"/>
       <c r="F114" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14"/>
       <c r="B115" s="11" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
       <c r="E115" s="16"/>
       <c r="F115" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14"/>
       <c r="B116" s="11" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D116" s="14"/>
       <c r="E116" s="16"/>
       <c r="F116" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14"/>
       <c r="B117" s="11" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
       <c r="E117" s="16"/>
       <c r="F117" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14"/>
       <c r="B118" s="11" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
       <c r="F118" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14"/>
       <c r="B119" s="11" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
       <c r="F119" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14"/>
       <c r="B120" s="11" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="121">
@@ -2709,10 +2709,10 @@
     <row r="122">
       <c r="A122" s="14"/>
       <c r="B122" s="11" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
@@ -2753,149 +2753,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>54</v>
+        <v>33</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="G8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>127</v>
+        <v>75</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="14">
       <c r="A14" s="13" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -3997,27 +3997,27 @@
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="17" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12"/>
       <c r="B101" s="13" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
@@ -4058,102 +4058,102 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>168</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>65</v>
+        <v>172</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>128</v>
+        <v>200</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -4161,44 +4161,44 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>138</v>
+        <v>208</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>144</v>
+        <v>222</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14">
@@ -4217,11 +4217,11 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="13" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -4629,27 +4629,27 @@
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="17" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12"/>
       <c r="B101" s="13" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
@@ -4692,34 +4692,34 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>177</v>
@@ -4730,125 +4730,125 @@
         <v>178</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>199</v>
+        <v>188</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>127</v>
+        <v>223</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>219</v>
+        <v>230</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="15">
@@ -4865,11 +4865,11 @@
     </row>
     <row r="16">
       <c r="A16" s="13" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -5217,27 +5217,27 @@
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="17" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12"/>
       <c r="B101" s="13" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
@@ -5282,149 +5282,149 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>220</v>
+        <v>196</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>245</v>
+        <v>233</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -5442,11 +5442,11 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="13" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -5876,27 +5876,27 @@
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="17" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12"/>
       <c r="B101" s="13" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
@@ -5939,65 +5939,65 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G6" s="6" t="s">
         <v>244</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="7">
@@ -6005,83 +6005,83 @@
         <v>246</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="14">
@@ -6100,11 +6100,11 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="13" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="13"/>
@@ -6568,27 +6568,27 @@
     </row>
     <row r="100">
       <c r="A100" s="13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="17" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12"/>
       <c r="B101" s="13" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
@@ -6626,18 +6626,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -6657,16 +6657,16 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>253</v>
+      <c r="A1" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
